--- a/product_surveys/028_milkshake_flavor_preference_survey--product_surveys.xlsx
+++ b/product_surveys/028_milkshake_flavor_preference_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>flavor_preferences</t>
+          <t>page1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Milkshake Flavors</t>
+          <t>What flavors do you like?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>satisfaction</t>
+          <t>page2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>How satisfied are you with our current milkshake flavors?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>new_offerings</t>
+          <t>page3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New Offerings</t>
+          <t>What flavors are you interested in trying?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>flavor_interest</t>
+          <t>page4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Which Milkshake Flavors Are You Interested In?</t>
+          <t>How satisfied are you with the flavor of your favorite milkshake?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>favorite_flavor</t>
+          <t>page5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Favorite Flavor</t>
+          <t>How interested are you in trying new milkshake flavors?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>new_flavor_interest</t>
+          <t>page6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New Flavor Interest</t>
+          <t>How much do you like the current flavor of our milkshake?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>flavor_demand</t>
+          <t>page7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Milkshake Flavor Demand</t>
+          <t>What is your favorite milkshake flavor?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>favorite_milkshake</t>
+          <t>page8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Favorite Milkshake</t>
+          <t>How would you rate your satisfaction with our milkshake flavors?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>flavor_satisfaction</t>
+          <t>page9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Flavor Satisfaction</t>
+          <t>How much do you like our milkshake flavors?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>new_flavor</t>
+          <t>page10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New Milkshake Flavor Interest</t>
+          <t>Page10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>milkshake_flavor_interest</t>
+          <t>page11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Milkshake Flavor Interest</t>
+          <t>Page11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,24 +768,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction</t>
+          <t>page12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Please enter a number between 1-10</t>
-        </is>
-      </c>
+          <t>Page12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -795,24 +791,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>milkshake_flavor_demand</t>
+          <t>page13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Milkshake Flavor Demand</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Please enter a number between 1.0-10.0</t>
-        </is>
-      </c>
+          <t>Page13</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -827,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>new_milkshake</t>
+          <t>page14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New Milkshake</t>
+          <t>Page14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -845,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>milkshake_interests</t>
+          <t>page15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Milkshake Interests</t>
+          <t>Page15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -868,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_2</t>
+          <t>page16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Page16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -896,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>milkshake_flavor_preferences_2</t>
+          <t>page17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milkshake Flavors</t>
+          <t>Page17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -919,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_2</t>
+          <t>page18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Page18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>milkshake_flavor_demand_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Milkshake Flavor Demand</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>milkshake_satisfaction_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Satisfaction</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>milkshake_flavor_preferences_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Milkshake Flavors</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>milkshake_satisfaction_4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Satisfaction</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>milkshake_flavor_preferences_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Milkshake Flavors</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>milkshake_satisfaction_5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Satisfaction</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>milkshake_flavor_preferences_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Milkshake Flavors</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1106,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1134,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>flavor_preferences_choices</t>
+          <t>page1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1151,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>flavor_preferences_choices</t>
+          <t>page1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1168,7 +999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>flavor_preferences_choices</t>
+          <t>page1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1185,7 +1016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>page2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1202,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>page2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1219,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>page2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1236,7 +1067,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>page2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>page2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1270,1173 +1101,1054 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>new_offerings_choices</t>
+          <t>page3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>very_interested</t>
+          <t>vanilla</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Very Interested</t>
+          <t>Vanilla</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>new_offerings_choices</t>
+          <t>page3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>somewhat_interested</t>
+          <t>chocolate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Somewhat Interested</t>
+          <t>Chocolate</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>new_offerings_choices</t>
+          <t>page3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_interested</t>
+          <t>strawberry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Not Interested</t>
+          <t>Strawberry</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>flavor_interest_choices</t>
+          <t>page4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>flavor_interest_choices</t>
+          <t>page4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>chocolate</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chocolate</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>flavor_interest_choices</t>
+          <t>page4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>strawberry</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Strawberry</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>favorite_flavor_choices</t>
+          <t>page4_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>favorite_flavor_choices</t>
+          <t>page4_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chocolate</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chocolate</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>favorite_flavor_choices</t>
+          <t>page5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>strawberry</t>
+          <t>very_interested</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Strawberry</t>
+          <t>Very Interested</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>new_flavor_interest_choices</t>
+          <t>page5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>very_interested</t>
+          <t>somewhat_interested</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Very Interested</t>
+          <t>Somewhat Interested</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>new_flavor_interest_choices</t>
+          <t>page5_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>somewhat_interested</t>
+          <t>not_interested</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Somewhat Interested</t>
+          <t>Not Interested</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>new_flavor_interest_choices</t>
+          <t>page6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_interested</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Not Interested</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>flavor_demand_choices</t>
+          <t>page6_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>flavor_demand_choices</t>
+          <t>page6_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>flavor_demand_choices</t>
+          <t>page7_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>vanilla</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Vanilla</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>favorite_milkshake_choices</t>
+          <t>page7_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>chocolate</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Chocolate</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>favorite_milkshake_choices</t>
+          <t>page7_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>chocolate</t>
+          <t>strawberry</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chocolate</t>
+          <t>Strawberry</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>favorite_milkshake_choices</t>
+          <t>page8_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>strawberry</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Strawberry</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>flavor_satisfaction_choices</t>
+          <t>page8_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>flavor_satisfaction_choices</t>
+          <t>page8_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>flavor_satisfaction_choices</t>
+          <t>page8_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>flavor_satisfaction_choices</t>
+          <t>page8_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Somewhat Dissatisfied</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>flavor_satisfaction_choices</t>
+          <t>page9_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Very Dissatisfied</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>new_flavor_choices</t>
+          <t>page9_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>very_interested</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Very Interested</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>new_flavor_choices</t>
+          <t>page9_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>somewhat_interested</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Somewhat Interested</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>new_flavor_choices</t>
+          <t>page10_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>not_interested</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Not Interested</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>new_milkshake_choices</t>
+          <t>page10_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>very_interested</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Very Interested</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>new_milkshake_choices</t>
+          <t>page10_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>somewhat_interested</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Somewhat Interested</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>new_milkshake_choices</t>
+          <t>page10_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>not_interested</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Not Interested</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_2_choices</t>
+          <t>page10_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_2_choices</t>
+          <t>page11_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>very_interested</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>Very Interested</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_2_choices</t>
+          <t>page11_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_interested</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat Interested</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_2_choices</t>
+          <t>page11_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>not_interested</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Somewhat Dissatisfied</t>
+          <t>Not Interested</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_2_choices</t>
+          <t>page12_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Very Dissatisfied</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>milkshake_flavor_preferences_2_choices</t>
+          <t>page12_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>milkshake_flavor_preferences_2_choices</t>
+          <t>page12_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>chocolate</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chocolate</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>milkshake_flavor_preferences_2_choices</t>
+          <t>page12_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>strawberry</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Strawberry</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_2_choices</t>
+          <t>page12_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_2_choices</t>
+          <t>page13_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_2_choices</t>
+          <t>page13_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_2_choices</t>
+          <t>page13_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Somewhat Dissatisfied</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_2_choices</t>
+          <t>page14_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Very Dissatisfied</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>milkshake_flavor_demand_2_choices</t>
+          <t>page14_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>milkshake_flavor_demand_2_choices</t>
+          <t>page14_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>milkshake_flavor_demand_2_choices</t>
+          <t>page14_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_3_choices</t>
+          <t>page14_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_3_choices</t>
+          <t>page15_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>very_interested</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>Very Interested</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_3_choices</t>
+          <t>page15_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_interested</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat Interested</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_3_choices</t>
+          <t>page15_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>not_interested</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Somewhat Dissatisfied</t>
+          <t>Not Interested</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_3_choices</t>
+          <t>page16_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Very Dissatisfied</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>milkshake_flavor_preferences_3_choices</t>
+          <t>page16_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>milkshake_flavor_preferences_3_choices</t>
+          <t>page16_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>chocolate</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chocolate</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>milkshake_flavor_preferences_3_choices</t>
+          <t>page16_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>strawberry</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Strawberry</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_4_choices</t>
+          <t>page16_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_4_choices</t>
+          <t>page17_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_4_choices</t>
+          <t>page17_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_4_choices</t>
+          <t>page17_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Somewhat Dissatisfied</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_4_choices</t>
+          <t>page18_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Very Dissatisfied</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>milkshake_flavor_preferences_4_choices</t>
+          <t>page18_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>milkshake_flavor_preferences_4_choices</t>
+          <t>page18_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>chocolate</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chocolate</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>milkshake_flavor_preferences_4_choices</t>
+          <t>page18_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>strawberry</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Strawberry</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>milkshake_satisfaction_5_choices</t>
+          <t>page18_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>milkshake_satisfaction_5_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>somewhat_satisfied</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Somewhat Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>milkshake_satisfaction_5_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>milkshake_satisfaction_5_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>somewhat_dissatisfied</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Somewhat Dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>milkshake_satisfaction_5_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>very_dissatisfied</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
           <t>Very Dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>milkshake_flavor_preferences_5_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>vanilla</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Vanilla</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>milkshake_flavor_preferences_5_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>chocolate</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Chocolate</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>milkshake_flavor_preferences_5_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>strawberry</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Strawberry</t>
         </is>
       </c>
     </row>
